--- a/final_data_pipeline/output/311611longform.xlsx
+++ b/final_data_pipeline/output/311611longform.xlsx
@@ -984,7 +984,7 @@
         <v>44138.20517500199</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -1073,7 +1073,7 @@
         <v>138</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1162,7 +1162,7 @@
         <v>138</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1251,7 +1251,7 @@
         <v>138</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1340,7 +1340,7 @@
         <v>138</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1429,7 +1429,7 @@
         <v>138</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1518,7 +1518,7 @@
         <v>138</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1607,7 +1607,7 @@
         <v>138</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1696,7 +1696,7 @@
         <v>138</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1785,7 +1785,7 @@
         <v>138</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1877,7 +1877,7 @@
         <v>138</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1969,7 +1969,7 @@
         <v>138</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -2058,7 +2058,7 @@
         <v>138</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2147,7 +2147,7 @@
         <v>138</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2236,7 +2236,7 @@
         <v>138</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -6081,7 +6081,7 @@
         <v>138</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6170,7 +6170,7 @@
         <v>138</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6259,7 +6259,7 @@
         <v>138</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6348,7 +6348,7 @@
         <v>138</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6440,7 +6440,7 @@
         <v>138</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6529,7 +6529,7 @@
         <v>138</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6618,7 +6618,7 @@
         <v>138</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6707,7 +6707,7 @@
         <v>138</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6796,7 +6796,7 @@
         <v>138</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -6885,7 +6885,7 @@
         <v>138</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -6974,7 +6974,7 @@
         <v>138</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -7063,7 +7063,7 @@
         <v>138</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7152,7 +7152,7 @@
         <v>138</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7244,7 +7244,7 @@
         <v>138</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -11908,7 +11908,7 @@
         <v>138</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -11997,7 +11997,7 @@
         <v>138</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12086,7 +12086,7 @@
         <v>138</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -12175,7 +12175,7 @@
         <v>138</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -12264,7 +12264,7 @@
         <v>138</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -12353,7 +12353,7 @@
         <v>138</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -12442,7 +12442,7 @@
         <v>138</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -12531,7 +12531,7 @@
         <v>138</v>
       </c>
       <c r="AA131">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB131">
         <v>8000</v>
@@ -12620,7 +12620,7 @@
         <v>138</v>
       </c>
       <c r="AA132">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB132">
         <v>8000</v>
@@ -12709,7 +12709,7 @@
         <v>138</v>
       </c>
       <c r="AA133">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB133">
         <v>8000</v>
@@ -12801,7 +12801,7 @@
         <v>138</v>
       </c>
       <c r="AA134">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB134">
         <v>8000</v>
@@ -12890,7 +12890,7 @@
         <v>138</v>
       </c>
       <c r="AA135">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB135">
         <v>8000</v>
@@ -12979,7 +12979,7 @@
         <v>138</v>
       </c>
       <c r="AA136">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB136">
         <v>8000</v>
@@ -13068,7 +13068,7 @@
         <v>138</v>
       </c>
       <c r="AA137">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB137">
         <v>8000</v>
@@ -15038,7 +15038,7 @@
         <v>138</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -15127,7 +15127,7 @@
         <v>138</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -15216,7 +15216,7 @@
         <v>138</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB161">
         <v>8000</v>
@@ -15305,7 +15305,7 @@
         <v>138</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -15394,7 +15394,7 @@
         <v>138</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -15483,7 +15483,7 @@
         <v>138</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -15572,7 +15572,7 @@
         <v>138</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -16916,7 +16916,7 @@
         <v>138</v>
       </c>
       <c r="AA180">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB180">
         <v>8000</v>
@@ -17008,7 +17008,7 @@
         <v>138</v>
       </c>
       <c r="AA181">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB181">
         <v>8000</v>
@@ -17097,7 +17097,7 @@
         <v>138</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -17186,7 +17186,7 @@
         <v>138</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -17275,7 +17275,7 @@
         <v>138</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -17364,7 +17364,7 @@
         <v>138</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB185">
         <v>8000</v>
@@ -17453,7 +17453,7 @@
         <v>138</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB186">
         <v>8000</v>
@@ -17542,7 +17542,7 @@
         <v>138</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB187">
         <v>8000</v>
@@ -17631,7 +17631,7 @@
         <v>138</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB188">
         <v>8000</v>
@@ -17720,7 +17720,7 @@
         <v>138</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB189">
         <v>8000</v>
@@ -17809,7 +17809,7 @@
         <v>138</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -17898,7 +17898,7 @@
         <v>138</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -17987,7 +17987,7 @@
         <v>138</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -18076,7 +18076,7 @@
         <v>138</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -19417,7 +19417,7 @@
         <v>138</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -19506,7 +19506,7 @@
         <v>138</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -19595,7 +19595,7 @@
         <v>138</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -19684,7 +19684,7 @@
         <v>138</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -19773,7 +19773,7 @@
         <v>138</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -19865,7 +19865,7 @@
         <v>138</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -19957,7 +19957,7 @@
         <v>138</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB214">
         <v>8000</v>
@@ -20046,7 +20046,7 @@
         <v>138</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB215">
         <v>8000</v>
@@ -20135,7 +20135,7 @@
         <v>138</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB216">
         <v>8000</v>
@@ -20224,7 +20224,7 @@
         <v>138</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB217">
         <v>8000</v>
@@ -20313,7 +20313,7 @@
         <v>138</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB218">
         <v>8000</v>
@@ -20402,7 +20402,7 @@
         <v>138</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB219">
         <v>8000</v>
@@ -20491,7 +20491,7 @@
         <v>138</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -20580,7 +20580,7 @@
         <v>138</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -21912,7 +21912,7 @@
         <v>31090.90891717494</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB236">
         <v>8000</v>
@@ -22001,7 +22001,7 @@
         <v>138</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB237">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>138</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -22179,7 +22179,7 @@
         <v>138</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -22268,7 +22268,7 @@
         <v>138</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -22357,7 +22357,7 @@
         <v>138</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -22446,7 +22446,7 @@
         <v>138</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -22538,7 +22538,7 @@
         <v>138</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -22630,7 +22630,7 @@
         <v>138</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -22719,7 +22719,7 @@
         <v>138</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -22808,7 +22808,7 @@
         <v>138</v>
       </c>
       <c r="AA246">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB246">
         <v>8000</v>
@@ -22897,7 +22897,7 @@
         <v>138</v>
       </c>
       <c r="AA247">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB247">
         <v>8000</v>
@@ -22986,7 +22986,7 @@
         <v>138</v>
       </c>
       <c r="AA248">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB248">
         <v>8000</v>
@@ -23075,7 +23075,7 @@
         <v>138</v>
       </c>
       <c r="AA249">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB249">
         <v>8000</v>
@@ -23164,7 +23164,7 @@
         <v>138</v>
       </c>
       <c r="AA250">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB250">
         <v>8000</v>
@@ -24505,7 +24505,7 @@
         <v>138</v>
       </c>
       <c r="AA265">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB265">
         <v>8000</v>
@@ -24594,7 +24594,7 @@
         <v>138</v>
       </c>
       <c r="AA266">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB266">
         <v>8000</v>
@@ -24683,7 +24683,7 @@
         <v>138</v>
       </c>
       <c r="AA267">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB267">
         <v>8000</v>
@@ -24775,7 +24775,7 @@
         <v>138</v>
       </c>
       <c r="AA268">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB268">
         <v>8000</v>
@@ -24864,7 +24864,7 @@
         <v>138</v>
       </c>
       <c r="AA269">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB269">
         <v>8000</v>
@@ -24953,7 +24953,7 @@
         <v>138</v>
       </c>
       <c r="AA270">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB270">
         <v>8000</v>
@@ -25042,7 +25042,7 @@
         <v>138</v>
       </c>
       <c r="AA271">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB271">
         <v>8000</v>
@@ -25757,7 +25757,7 @@
         <v>138</v>
       </c>
       <c r="AA279">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB279">
         <v>8000</v>
@@ -25846,7 +25846,7 @@
         <v>138</v>
       </c>
       <c r="AA280">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB280">
         <v>8000</v>
@@ -25935,7 +25935,7 @@
         <v>138</v>
       </c>
       <c r="AA281">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB281">
         <v>8000</v>
@@ -26024,7 +26024,7 @@
         <v>138</v>
       </c>
       <c r="AA282">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB282">
         <v>8000</v>
@@ -26113,7 +26113,7 @@
         <v>138</v>
       </c>
       <c r="AA283">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB283">
         <v>8000</v>
@@ -26205,7 +26205,7 @@
         <v>138</v>
       </c>
       <c r="AA284">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB284">
         <v>8000</v>
@@ -26294,7 +26294,7 @@
         <v>138</v>
       </c>
       <c r="AA285">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB285">
         <v>8000</v>
@@ -26383,7 +26383,7 @@
         <v>138</v>
       </c>
       <c r="AA286">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB286">
         <v>8000</v>
@@ -26472,7 +26472,7 @@
         <v>138</v>
       </c>
       <c r="AA287">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB287">
         <v>8000</v>
@@ -26561,7 +26561,7 @@
         <v>138</v>
       </c>
       <c r="AA288">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB288">
         <v>8000</v>
@@ -26650,7 +26650,7 @@
         <v>138</v>
       </c>
       <c r="AA289">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB289">
         <v>8000</v>
@@ -26739,7 +26739,7 @@
         <v>138</v>
       </c>
       <c r="AA290">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB290">
         <v>8000</v>
@@ -26828,7 +26828,7 @@
         <v>138</v>
       </c>
       <c r="AA291">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB291">
         <v>8000</v>
@@ -26917,7 +26917,7 @@
         <v>138</v>
       </c>
       <c r="AA292">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB292">
         <v>8000</v>
@@ -27006,7 +27006,7 @@
         <v>138</v>
       </c>
       <c r="AA293">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB293">
         <v>8000</v>
@@ -27095,7 +27095,7 @@
         <v>138</v>
       </c>
       <c r="AA294">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB294">
         <v>8000</v>
@@ -27184,7 +27184,7 @@
         <v>138</v>
       </c>
       <c r="AA295">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB295">
         <v>8000</v>
@@ -27273,7 +27273,7 @@
         <v>138</v>
       </c>
       <c r="AA296">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB296">
         <v>8000</v>
@@ -27362,7 +27362,7 @@
         <v>138</v>
       </c>
       <c r="AA297">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB297">
         <v>8000</v>
@@ -27454,7 +27454,7 @@
         <v>138</v>
       </c>
       <c r="AA298">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB298">
         <v>8000</v>
@@ -27546,7 +27546,7 @@
         <v>138</v>
       </c>
       <c r="AA299">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB299">
         <v>8000</v>
@@ -27638,7 +27638,7 @@
         <v>138</v>
       </c>
       <c r="AA300">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB300">
         <v>8000</v>
@@ -27730,7 +27730,7 @@
         <v>138</v>
       </c>
       <c r="AA301">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB301">
         <v>8000</v>
@@ -27819,7 +27819,7 @@
         <v>138</v>
       </c>
       <c r="AA302">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB302">
         <v>8000</v>
@@ -27908,7 +27908,7 @@
         <v>138</v>
       </c>
       <c r="AA303">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB303">
         <v>8000</v>
@@ -27997,7 +27997,7 @@
         <v>138</v>
       </c>
       <c r="AA304">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB304">
         <v>8000</v>
@@ -28086,7 +28086,7 @@
         <v>138</v>
       </c>
       <c r="AA305">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB305">
         <v>8000</v>
@@ -28175,7 +28175,7 @@
         <v>138</v>
       </c>
       <c r="AA306">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB306">
         <v>8000</v>
@@ -28264,7 +28264,7 @@
         <v>138</v>
       </c>
       <c r="AA307">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB307">
         <v>8000</v>
@@ -28356,7 +28356,7 @@
         <v>138</v>
       </c>
       <c r="AA308">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB308">
         <v>8000</v>
@@ -28445,7 +28445,7 @@
         <v>138</v>
       </c>
       <c r="AA309">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB309">
         <v>8000</v>
@@ -28534,7 +28534,7 @@
         <v>138</v>
       </c>
       <c r="AA310">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB310">
         <v>8000</v>
@@ -28623,7 +28623,7 @@
         <v>138</v>
       </c>
       <c r="AA311">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB311">
         <v>8000</v>
@@ -28712,7 +28712,7 @@
         <v>138</v>
       </c>
       <c r="AA312">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB312">
         <v>8000</v>
@@ -28801,7 +28801,7 @@
         <v>138</v>
       </c>
       <c r="AA313">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB313">
         <v>8000</v>
@@ -28890,7 +28890,7 @@
         <v>138</v>
       </c>
       <c r="AA314">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB314">
         <v>8000</v>
@@ -28979,7 +28979,7 @@
         <v>138</v>
       </c>
       <c r="AA315">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB315">
         <v>8000</v>
@@ -29068,7 +29068,7 @@
         <v>138</v>
       </c>
       <c r="AA316">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB316">
         <v>8000</v>
@@ -29157,7 +29157,7 @@
         <v>138</v>
       </c>
       <c r="AA317">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB317">
         <v>8000</v>
@@ -29246,7 +29246,7 @@
         <v>138</v>
       </c>
       <c r="AA318">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB318">
         <v>8000</v>
@@ -29335,7 +29335,7 @@
         <v>138</v>
       </c>
       <c r="AA319">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB319">
         <v>8000</v>
@@ -29424,7 +29424,7 @@
         <v>138</v>
       </c>
       <c r="AA320">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB320">
         <v>8000</v>
@@ -29516,7 +29516,7 @@
         <v>138</v>
       </c>
       <c r="AA321">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB321">
         <v>8000</v>
@@ -29605,7 +29605,7 @@
         <v>138</v>
       </c>
       <c r="AA322">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB322">
         <v>8000</v>
@@ -29694,7 +29694,7 @@
         <v>138</v>
       </c>
       <c r="AA323">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB323">
         <v>8000</v>
@@ -29783,7 +29783,7 @@
         <v>138</v>
       </c>
       <c r="AA324">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB324">
         <v>8000</v>
@@ -29872,7 +29872,7 @@
         <v>138</v>
       </c>
       <c r="AA325">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB325">
         <v>8000</v>
@@ -29961,7 +29961,7 @@
         <v>138</v>
       </c>
       <c r="AA326">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB326">
         <v>8000</v>
@@ -30053,7 +30053,7 @@
         <v>138</v>
       </c>
       <c r="AA327">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB327">
         <v>8000</v>
@@ -30142,7 +30142,7 @@
         <v>138</v>
       </c>
       <c r="AA328">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB328">
         <v>8000</v>
@@ -30231,7 +30231,7 @@
         <v>138</v>
       </c>
       <c r="AA329">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB329">
         <v>8000</v>
@@ -30320,7 +30320,7 @@
         <v>138</v>
       </c>
       <c r="AA330">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB330">
         <v>8000</v>
@@ -30409,7 +30409,7 @@
         <v>138</v>
       </c>
       <c r="AA331">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB331">
         <v>8000</v>
@@ -30498,7 +30498,7 @@
         <v>138</v>
       </c>
       <c r="AA332">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB332">
         <v>8000</v>
@@ -30587,7 +30587,7 @@
         <v>138</v>
       </c>
       <c r="AA333">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB333">
         <v>8000</v>
@@ -30676,7 +30676,7 @@
         <v>138</v>
       </c>
       <c r="AA334">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AB334">
         <v>8000</v>
@@ -30765,7 +30765,7 @@
         <v>138</v>
       </c>
       <c r="AA335">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB335">
         <v>8000</v>
@@ -30857,7 +30857,7 @@
         <v>138</v>
       </c>
       <c r="AA336">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB336">
         <v>8000</v>
@@ -30946,7 +30946,7 @@
         <v>138</v>
       </c>
       <c r="AA337">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB337">
         <v>8000</v>
@@ -31035,7 +31035,7 @@
         <v>138</v>
       </c>
       <c r="AA338">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB338">
         <v>8000</v>
@@ -31127,7 +31127,7 @@
         <v>138</v>
       </c>
       <c r="AA339">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB339">
         <v>8000</v>
@@ -31216,7 +31216,7 @@
         <v>138</v>
       </c>
       <c r="AA340">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB340">
         <v>8000</v>
@@ -31305,7 +31305,7 @@
         <v>138</v>
       </c>
       <c r="AA341">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB341">
         <v>8000</v>
@@ -31394,7 +31394,7 @@
         <v>138</v>
       </c>
       <c r="AA342">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB342">
         <v>8000</v>
@@ -31483,7 +31483,7 @@
         <v>138</v>
       </c>
       <c r="AA343">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB343">
         <v>8000</v>
@@ -31572,7 +31572,7 @@
         <v>138</v>
       </c>
       <c r="AA344">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB344">
         <v>8000</v>
@@ -31661,7 +31661,7 @@
         <v>138</v>
       </c>
       <c r="AA345">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB345">
         <v>8000</v>
@@ -31750,7 +31750,7 @@
         <v>138</v>
       </c>
       <c r="AA346">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB346">
         <v>8000</v>
@@ -31839,7 +31839,7 @@
         <v>138</v>
       </c>
       <c r="AA347">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB347">
         <v>8000</v>
@@ -31928,7 +31928,7 @@
         <v>138</v>
       </c>
       <c r="AA348">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB348">
         <v>8000</v>
@@ -37731,7 +37731,7 @@
         <v>138</v>
       </c>
       <c r="AA413">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB413">
         <v>8000</v>
@@ -37820,7 +37820,7 @@
         <v>138</v>
       </c>
       <c r="AA414">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB414">
         <v>8000</v>
@@ -37912,7 +37912,7 @@
         <v>138</v>
       </c>
       <c r="AA415">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB415">
         <v>8000</v>
@@ -38004,7 +38004,7 @@
         <v>138</v>
       </c>
       <c r="AA416">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB416">
         <v>8000</v>
@@ -38093,7 +38093,7 @@
         <v>138</v>
       </c>
       <c r="AA417">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB417">
         <v>8000</v>
@@ -38182,7 +38182,7 @@
         <v>138</v>
       </c>
       <c r="AA418">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB418">
         <v>8000</v>
@@ -38271,7 +38271,7 @@
         <v>138</v>
       </c>
       <c r="AA419">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB419">
         <v>8000</v>
@@ -38360,7 +38360,7 @@
         <v>138</v>
       </c>
       <c r="AA420">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB420">
         <v>8000</v>
@@ -38449,7 +38449,7 @@
         <v>138</v>
       </c>
       <c r="AA421">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB421">
         <v>8000</v>
@@ -38538,7 +38538,7 @@
         <v>138</v>
       </c>
       <c r="AA422">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB422">
         <v>8000</v>
@@ -38627,7 +38627,7 @@
         <v>138</v>
       </c>
       <c r="AA423">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB423">
         <v>8000</v>
@@ -38716,7 +38716,7 @@
         <v>138</v>
       </c>
       <c r="AA424">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB424">
         <v>8000</v>
@@ -38805,7 +38805,7 @@
         <v>138</v>
       </c>
       <c r="AA425">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB425">
         <v>8000</v>
@@ -38894,7 +38894,7 @@
         <v>138</v>
       </c>
       <c r="AA426">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB426">
         <v>8000</v>
@@ -38983,7 +38983,7 @@
         <v>138</v>
       </c>
       <c r="AA427">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB427">
         <v>8000</v>
@@ -39072,7 +39072,7 @@
         <v>138</v>
       </c>
       <c r="AA428">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB428">
         <v>8000</v>
@@ -39161,7 +39161,7 @@
         <v>138</v>
       </c>
       <c r="AA429">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB429">
         <v>8000</v>
@@ -39250,7 +39250,7 @@
         <v>138</v>
       </c>
       <c r="AA430">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB430">
         <v>8000</v>
@@ -39339,7 +39339,7 @@
         <v>138</v>
       </c>
       <c r="AA431">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB431">
         <v>8000</v>
@@ -39431,7 +39431,7 @@
         <v>138</v>
       </c>
       <c r="AA432">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB432">
         <v>8000</v>
@@ -39523,7 +39523,7 @@
         <v>138</v>
       </c>
       <c r="AA433">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB433">
         <v>8000</v>
@@ -39615,7 +39615,7 @@
         <v>138</v>
       </c>
       <c r="AA434">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB434">
         <v>8000</v>
@@ -39704,7 +39704,7 @@
         <v>138</v>
       </c>
       <c r="AA435">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB435">
         <v>8000</v>
@@ -39793,7 +39793,7 @@
         <v>138</v>
       </c>
       <c r="AA436">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB436">
         <v>8000</v>
@@ -39882,7 +39882,7 @@
         <v>138</v>
       </c>
       <c r="AA437">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB437">
         <v>8000</v>
@@ -39971,7 +39971,7 @@
         <v>138</v>
       </c>
       <c r="AA438">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB438">
         <v>8000</v>
@@ -40060,7 +40060,7 @@
         <v>138</v>
       </c>
       <c r="AA439">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB439">
         <v>8000</v>
@@ -40149,7 +40149,7 @@
         <v>138</v>
       </c>
       <c r="AA440">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB440">
         <v>8000</v>
@@ -40238,7 +40238,7 @@
         <v>138</v>
       </c>
       <c r="AA441">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB441">
         <v>8000</v>
@@ -40327,7 +40327,7 @@
         <v>138</v>
       </c>
       <c r="AA442">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB442">
         <v>8000</v>
@@ -40416,7 +40416,7 @@
         <v>138</v>
       </c>
       <c r="AA443">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB443">
         <v>8000</v>
@@ -40505,7 +40505,7 @@
         <v>138</v>
       </c>
       <c r="AA444">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB444">
         <v>8000</v>
@@ -40594,7 +40594,7 @@
         <v>138</v>
       </c>
       <c r="AA445">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB445">
         <v>8000</v>
@@ -40683,7 +40683,7 @@
         <v>138</v>
       </c>
       <c r="AA446">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB446">
         <v>8000</v>
@@ -40772,7 +40772,7 @@
         <v>138</v>
       </c>
       <c r="AA447">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB447">
         <v>8000</v>
@@ -40861,7 +40861,7 @@
         <v>138</v>
       </c>
       <c r="AA448">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB448">
         <v>8000</v>
@@ -40950,7 +40950,7 @@
         <v>138</v>
       </c>
       <c r="AA449">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB449">
         <v>8000</v>
@@ -41039,7 +41039,7 @@
         <v>138</v>
       </c>
       <c r="AA450">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB450">
         <v>8000</v>
@@ -41128,7 +41128,7 @@
         <v>138</v>
       </c>
       <c r="AA451">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB451">
         <v>8000</v>
@@ -41217,7 +41217,7 @@
         <v>138</v>
       </c>
       <c r="AA452">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB452">
         <v>8000</v>
@@ -41306,7 +41306,7 @@
         <v>138</v>
       </c>
       <c r="AA453">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB453">
         <v>8000</v>
@@ -41398,7 +41398,7 @@
         <v>138</v>
       </c>
       <c r="AA454">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB454">
         <v>8000</v>
@@ -41487,7 +41487,7 @@
         <v>138</v>
       </c>
       <c r="AA455">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB455">
         <v>8000</v>
@@ -41576,7 +41576,7 @@
         <v>138</v>
       </c>
       <c r="AA456">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB456">
         <v>8000</v>
@@ -41665,7 +41665,7 @@
         <v>138</v>
       </c>
       <c r="AA457">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB457">
         <v>8000</v>
@@ -41754,7 +41754,7 @@
         <v>138</v>
       </c>
       <c r="AA458">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB458">
         <v>8000</v>
@@ -41843,7 +41843,7 @@
         <v>138</v>
       </c>
       <c r="AA459">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB459">
         <v>8000</v>
@@ -41932,7 +41932,7 @@
         <v>138</v>
       </c>
       <c r="AA460">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB460">
         <v>8000</v>
@@ -42024,7 +42024,7 @@
         <v>138</v>
       </c>
       <c r="AA461">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB461">
         <v>8000</v>
@@ -43365,7 +43365,7 @@
         <v>138</v>
       </c>
       <c r="AA476">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB476">
         <v>8000</v>
@@ -43454,7 +43454,7 @@
         <v>138</v>
       </c>
       <c r="AA477">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB477">
         <v>8000</v>
@@ -43546,7 +43546,7 @@
         <v>138</v>
       </c>
       <c r="AA478">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB478">
         <v>8000</v>
@@ -43635,7 +43635,7 @@
         <v>138</v>
       </c>
       <c r="AA479">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB479">
         <v>8000</v>
@@ -43724,7 +43724,7 @@
         <v>138</v>
       </c>
       <c r="AA480">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB480">
         <v>8000</v>
@@ -43813,7 +43813,7 @@
         <v>138</v>
       </c>
       <c r="AA481">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB481">
         <v>8000</v>
@@ -43902,7 +43902,7 @@
         <v>138</v>
       </c>
       <c r="AA482">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB482">
         <v>8000</v>
@@ -43991,7 +43991,7 @@
         <v>138</v>
       </c>
       <c r="AA483">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB483">
         <v>8000</v>
@@ -44080,7 +44080,7 @@
         <v>138</v>
       </c>
       <c r="AA484">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB484">
         <v>8000</v>
@@ -44169,7 +44169,7 @@
         <v>138</v>
       </c>
       <c r="AA485">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB485">
         <v>8000</v>
@@ -44258,7 +44258,7 @@
         <v>138</v>
       </c>
       <c r="AA486">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB486">
         <v>8000</v>
@@ -44347,7 +44347,7 @@
         <v>138</v>
       </c>
       <c r="AA487">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB487">
         <v>8000</v>
@@ -44436,7 +44436,7 @@
         <v>138</v>
       </c>
       <c r="AA488">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB488">
         <v>8000</v>
@@ -44525,7 +44525,7 @@
         <v>138</v>
       </c>
       <c r="AA489">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB489">
         <v>8000</v>
@@ -44614,7 +44614,7 @@
         <v>138</v>
       </c>
       <c r="AA490">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB490">
         <v>8000</v>
@@ -44703,7 +44703,7 @@
         <v>138</v>
       </c>
       <c r="AA491">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB491">
         <v>8000</v>
@@ -44792,7 +44792,7 @@
         <v>138</v>
       </c>
       <c r="AA492">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB492">
         <v>8000</v>
@@ -44884,7 +44884,7 @@
         <v>138</v>
       </c>
       <c r="AA493">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB493">
         <v>8000</v>
@@ -44976,7 +44976,7 @@
         <v>138</v>
       </c>
       <c r="AA494">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB494">
         <v>8000</v>
@@ -45065,7 +45065,7 @@
         <v>138</v>
       </c>
       <c r="AA495">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB495">
         <v>8000</v>
@@ -45154,7 +45154,7 @@
         <v>138</v>
       </c>
       <c r="AA496">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB496">
         <v>8000</v>
